--- a/fhir/StructureDefinition-ehealth-practitioner.xlsx
+++ b/fhir/StructureDefinition-ehealth-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="367">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -913,6 +913,228 @@
   <si>
     <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence</t>
+  </si>
+  <si>
+    <t>decentralizedCompetence</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.identifier.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.identifier.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.identifier.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.identifier.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.identifier.use</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.identifier.type</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.identifier.type</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.identifier.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://ehealth.sundhed.dk/fhir/system/decentralized-competence</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>./IdentifierType</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.identifier.value</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>./Value</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.identifier.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.identifier.period</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>./StartDate and ./EndDate</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.identifier.assigner</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.identifier.assigner</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>./IdentifierIssuingAuthority</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.code</t>
+  </si>
+  <si>
+    <t>http://ehealth.sundhed.dk/vs/practitioner-competences</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:decentralizedCompetence.issuer</t>
   </si>
   <si>
     <t>Practitioner.communication</t>
@@ -1234,11 +1456,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN36"/>
+  <dimension ref="A1:AN52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.3203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.8984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.0703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.89453125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.7890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1256,12 +1478,12 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="49.78125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="51.5" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.953125" customWidth="true" bestFit="true"/>
@@ -1273,7 +1495,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="26.65625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="47.515625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="44.90625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -5273,9 +5495,11 @@
         <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>75</v>
       </c>
@@ -5296,20 +5520,16 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
       </c>
@@ -5333,13 +5553,13 @@
         <v>75</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>75</v>
@@ -5357,7 +5577,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>285</v>
+        <v>221</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5372,15 +5592,1837 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="B40" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="B41" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y49" s="2"/>
+      <c r="Z49" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>75</v>
       </c>
     </row>

--- a/fhir/StructureDefinition-ehealth-practitioner.xlsx
+++ b/fhir/StructureDefinition-ehealth-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-practitioner.xlsx
+++ b/fhir/StructureDefinition-ehealth-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-practitioner.xlsx
+++ b/fhir/StructureDefinition-ehealth-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-practitioner.xlsx
+++ b/fhir/StructureDefinition-ehealth-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-practitioner.xlsx
+++ b/fhir/StructureDefinition-ehealth-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-practitioner.xlsx
+++ b/fhir/StructureDefinition-ehealth-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
